--- a/Result/profitability/2013.xlsx
+++ b/Result/profitability/2013.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.7275</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7775</v>
+        <v>4.74375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6725</v>
+        <v>0.6825</v>
       </c>
       <c r="N3" t="n">
-        <v>4.44</v>
+        <v>4.4175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6425</v>
+        <v>0.66125</v>
       </c>
       <c r="N4" t="n">
-        <v>4.17125</v>
+        <v>4.23375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58875</v>
+        <v>0.5937500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>4.105</v>
+        <v>4.19125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5437500000000001</v>
+        <v>0.5287500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>4.0675</v>
+        <v>4.07125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4475</v>
+        <v>0.42875</v>
       </c>
       <c r="N7" t="n">
-        <v>4.0725</v>
+        <v>4.17625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.36875</v>
+        <v>0.38375</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1025</v>
+        <v>4.14625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5020</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4757</v>
+      </c>
+      <c r="E75" t="n">
+        <v>262</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>170</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>189</v>
+      </c>
+      <c r="K75" t="n">
+        <v>155</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.75875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.98625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1818181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3500000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07172131147541005</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.05405405405405417</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.6900000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1519823788546257</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
